--- a/data/trans_dic/IQ2606_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ2606_R2-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79,42%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>63,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>64,72%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57,97%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,25; 70,95</t>
+          <t>44,42; 61,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,54; 74,84</t>
+          <t>47,74; 67,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,67; 98,06</t>
+          <t>56,58; 92,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,84; 61,66</t>
+          <t>54,37; 70,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,65; 68,21</t>
+          <t>53,95; 74,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,59; 92,84</t>
+          <t>44,54; 95,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,21; 64,48</t>
+          <t>51,96; 64,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,11; 68,14</t>
+          <t>53,94; 68,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,64; 91,72</t>
+          <t>60,85; 90,17</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>55,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>72,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>59,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>72,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>84,19%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 62,77</t>
+          <t>51,44; 59,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,67; 75,61</t>
+          <t>68,77; 75,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,75; 90,26</t>
+          <t>79,24; 90,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,32; 58,68</t>
+          <t>55,41; 62,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,76; 75,58</t>
+          <t>68,89; 75,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,89; 90,67</t>
+          <t>74,95; 89,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,22; 59,57</t>
+          <t>54,34; 59,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,85; 74,61</t>
+          <t>69,74; 74,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,06; 89,11</t>
+          <t>80,37; 88,63</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81,78%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>70,11%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>78,08%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,67; 75,94</t>
+          <t>60,55; 72,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,54; 82,85</t>
+          <t>76,81; 86,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,62; 90,33</t>
+          <t>75,5; 94,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,11; 72,34</t>
+          <t>63,99; 75,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,15; 86,0</t>
+          <t>72,12; 82,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,98; 94,12</t>
+          <t>71,66; 90,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,03; 72,71</t>
+          <t>64,27; 72,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,23; 83,59</t>
+          <t>76,33; 83,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,74; 90,42</t>
+          <t>77,26; 90,54</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,02; 65,05</t>
+          <t>54,67; 60,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 75,94</t>
+          <t>70,58; 76,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,18; 88,21</t>
+          <t>80,69; 89,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,12; 60,55</t>
+          <t>58,64; 64,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,62; 75,96</t>
+          <t>69,98; 75,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,75; 89,91</t>
+          <t>77,03; 87,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,72; 61,83</t>
+          <t>57,77; 61,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,07; 75,01</t>
+          <t>71,28; 75,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,58; 87,88</t>
+          <t>80,46; 87,75</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45419</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39778</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9843</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>56774</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>38062</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45419</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>39778</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>15720</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48888; 63944</t>
+          <t>38010; 52888</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31485; 44014</t>
+          <t>32758; 46453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5600; 10427</t>
+          <t>7012; 11513</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37511; 52759</t>
+          <t>49001; 63717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32696; 46800</t>
+          <t>31727; 43831</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8518; 12838</t>
+          <t>3422; 7327</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91720; 113282</t>
+          <t>91291; 112493</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67669; 86827</t>
+          <t>68727; 87330</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16057; 22436</t>
+          <t>12217; 18103</t>
         </is>
       </c>
     </row>
@@ -1368,27 +1368,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>513</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>262567</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>351786</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105509</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>259347</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>336723</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74582</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>262567</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>351786</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>189094</t>
+          <t>178413</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>242402; 275833</t>
+          <t>244780; 281719</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>319932; 352263</t>
+          <t>334110; 366981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67995; 79962</t>
+          <t>97378; 111439</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>244172; 279221</t>
+          <t>243494; 276056</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>334064; 367172</t>
+          <t>320940; 352806</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>106430; 120791</t>
+          <t>65636; 78161</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>496201; 545200</t>
+          <t>497318; 547131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>664782; 710103</t>
+          <t>663687; 710782</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>179793; 197653</t>
+          <t>169142; 186531</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109025</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149031</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37454</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>112314</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>131841</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35838</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>109025</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>149031</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38753</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74592</t>
+          <t>73614</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>101987; 121652</t>
+          <t>98958; 118035</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122490; 139899</t>
+          <t>139973; 157072</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30974; 39067</t>
+          <t>32526; 40666</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98245; 118223</t>
+          <t>102509; 121643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>138757; 156711</t>
+          <t>121788; 139969</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32637; 42092</t>
+          <t>31282; 39498</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>207206; 235314</t>
+          <t>207991; 235333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>267621; 293458</t>
+          <t>267992; 294448</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67511; 79538</t>
+          <t>67017; 78529</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>186</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>417010</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>417010</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>407089; 448689</t>
+          <t>396288; 440769</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>487730; 526672</t>
+          <t>519925; 560415</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111389; 125669</t>
+          <t>143923; 160044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>392251; 438871</t>
+          <t>404431; 447552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>520202; 559587</t>
+          <t>485312; 524695</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>154849; 172418</t>
+          <t>107006; 121901</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>816512; 874557</t>
+          <t>817245; 875733</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1016482; 1072821</t>
+          <t>1019468; 1074166</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>272672; 293736</t>
+          <t>255275; 278403</t>
         </is>
       </c>
     </row>
